--- a/Analysis 2025.xlsx
+++ b/Analysis 2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,60 +501,110 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Rank_Spearman_Rating_Stat</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Rank_Spearman_Rating_PValue</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Rank_Kendall_Stat</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Rank_Kendall_PValue</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Rank_Kendall_Rating_Stat</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Rank_Kendall_Rating_PValue</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Top_5_5</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Top_5_25</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Top_10_10</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Top_10_50</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Top_20_20</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Top_20_50</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Top_5_5 (rating)</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Top_5_25 (rating)</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Top_10_10 (rating)</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Top_10_50 (rating)</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Top_20_20 (rating)</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Top_20_50 (rating)</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>TruePositives</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>FalsePositives</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>FalseNegatives</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>TrueNegatives</t>
         </is>
@@ -609,39 +659,69 @@
         <v>0.001261432915132484</v>
       </c>
       <c r="P2" t="n">
+        <v>0.2457725772577258</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.01371064919223499</v>
+      </c>
+      <c r="R2" t="n">
         <v>0.2161616161616162</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.001439631971375693</v>
       </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
+        <v>0.1676767676767677</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.01344208151005678</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>3</v>
       </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
         <v>6</v>
       </c>
-      <c r="V2" t="n">
+      <c r="Z2" t="n">
         <v>10</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AA2" t="n">
         <v>15</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH2" t="n">
         <v>56</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>44</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AK2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -694,39 +774,69 @@
         <v>0.0126887024418079</v>
       </c>
       <c r="P3" t="n">
+        <v>0.1284724799010513</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.205044620983137</v>
+      </c>
+      <c r="R3" t="n">
         <v>0.1556380127808699</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.02246177033904977</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0.09132137703566276</v>
       </c>
       <c r="U3" t="n">
+        <v>0.1804896316044494</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
         <v>4</v>
       </c>
-      <c r="V3" t="n">
+      <c r="Z3" t="n">
         <v>4</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AA3" t="n">
         <v>13</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH3" t="n">
         <v>56</v>
       </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>43</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AK3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -779,39 +889,69 @@
         <v>0.01250066727847989</v>
       </c>
       <c r="P4" t="n">
+        <v>0.1863546354635464</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.06339452024756959</v>
+      </c>
+      <c r="R4" t="n">
         <v>0.1535353535353536</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.02361296693368131</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0.1183838383838384</v>
       </c>
       <c r="U4" t="n">
+        <v>0.08095416139151809</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
         <v>8</v>
       </c>
-      <c r="V4" t="n">
+      <c r="Z4" t="n">
         <v>4</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AA4" t="n">
         <v>13</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH4" t="n">
         <v>56</v>
       </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>44</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AK4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -864,39 +1004,69 @@
         <v>0.04616970318782704</v>
       </c>
       <c r="P5" t="n">
+        <v>0.1892709270927093</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.05929519432270482</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.1345454545454546</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>0.0473198897932448</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
       <c r="T5" t="n">
+        <v>0.1280808080808081</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.05900903133812009</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
         <v>2</v>
       </c>
-      <c r="U5" t="n">
+      <c r="Y5" t="n">
         <v>8</v>
       </c>
-      <c r="V5" t="n">
+      <c r="Z5" t="n">
         <v>7</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AA5" t="n">
         <v>14</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH5" t="n">
         <v>56</v>
       </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>44</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AK5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -949,39 +1119,69 @@
         <v>0.04332839814186717</v>
       </c>
       <c r="P6" t="n">
+        <v>0.1201484230055659</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.2361852173243067</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.1309008451865595</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>0.05489694457397477</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
+        <v>0.08266336837765409</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.2254062523315611</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
         <v>2</v>
       </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>6</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Z6" t="n">
         <v>6</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AA6" t="n">
         <v>14</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH6" t="n">
         <v>55</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="AI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>44</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AK6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1034,39 +1234,69 @@
         <v>0.1537264127115947</v>
       </c>
       <c r="P7" t="n">
+        <v>0.1138553855385538</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.2593572592628849</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.0985858585858586</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.1461346514236891</v>
       </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
+        <v>0.08767676767676769</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.1961831164023432</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>2</v>
       </c>
-      <c r="T7" t="n">
+      <c r="X7" t="n">
         <v>2</v>
       </c>
-      <c r="U7" t="n">
+      <c r="Y7" t="n">
         <v>8</v>
       </c>
-      <c r="V7" t="n">
+      <c r="Z7" t="n">
         <v>5</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AA7" t="n">
         <v>14</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH7" t="n">
         <v>56</v>
       </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>44</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AK7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1119,39 +1349,69 @@
         <v>0.03458388399209721</v>
       </c>
       <c r="P8" t="n">
+        <v>0.1437023702370237</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.153761137996567</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.1426262626262626</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.03550508500881739</v>
       </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
+        <v>0.09010101010101011</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.1840988051963011</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="X8" t="n">
         <v>2</v>
       </c>
-      <c r="U8" t="n">
+      <c r="Y8" t="n">
         <v>7</v>
       </c>
-      <c r="V8" t="n">
+      <c r="Z8" t="n">
         <v>6</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AA8" t="n">
         <v>12</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH8" t="n">
         <v>55</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
+      <c r="AI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>43</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AK8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1204,39 +1464,69 @@
         <v>0.005649307188132052</v>
       </c>
       <c r="P9" t="n">
+        <v>0.2307110711071107</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.02092403460035088</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.1822222222222223</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.007225654722718255</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.1466666666666667</v>
       </c>
       <c r="U9" t="n">
+        <v>0.03060948358261464</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
         <v>5</v>
       </c>
-      <c r="V9" t="n">
+      <c r="Z9" t="n">
         <v>4</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AA9" t="n">
         <v>13</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH9" t="n">
         <v>56</v>
       </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>43</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AK9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1289,39 +1579,69 @@
         <v>0.1148284495756125</v>
       </c>
       <c r="P10" t="n">
+        <v>0.09725772577257724</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.3357311909923421</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.1034343434343434</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>0.1273100390036617</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
+        <v>0.07030303030303031</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.3000227323383703</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
         <v>2</v>
       </c>
-      <c r="T10" t="n">
+      <c r="X10" t="n">
         <v>2</v>
       </c>
-      <c r="U10" t="n">
+      <c r="Y10" t="n">
         <v>6</v>
       </c>
-      <c r="V10" t="n">
+      <c r="Z10" t="n">
         <v>5</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AA10" t="n">
         <v>13</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH10" t="n">
         <v>56</v>
       </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>44</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AK10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1374,39 +1694,69 @@
         <v>0.8655480107994523</v>
       </c>
       <c r="P11" t="n">
+        <v>0.1267080745341615</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.231369065746951</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.01391941391941392</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>0.8450714358982988</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.08669108669108669</v>
       </c>
       <c r="U11" t="n">
+        <v>0.2235921966045354</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
         <v>5</v>
       </c>
-      <c r="V11" t="n">
+      <c r="Z11" t="n">
         <v>3</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AA11" t="n">
         <v>8</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH11" t="n">
         <v>52</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AI11" t="n">
         <v>4</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AJ11" t="n">
         <v>39</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AK11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1459,39 +1809,69 @@
         <v>0.4203329445164341</v>
       </c>
       <c r="P12" t="n">
+        <v>0.04701573521432448</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.6491987862418123</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.05877192982456139</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.3962806539115912</v>
       </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
+        <v>0.03596491228070175</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.603692225651151</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
         <v>5</v>
       </c>
-      <c r="V12" t="n">
+      <c r="Z12" t="n">
         <v>4</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AA12" t="n">
         <v>10</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH12" t="n">
         <v>53</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AI12" t="n">
         <v>3</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AJ12" t="n">
         <v>43</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AK12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1544,39 +1924,69 @@
         <v>0.6419341035042265</v>
       </c>
       <c r="P13" t="n">
+        <v>0.03363107192267722</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.7423431836622821</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.02798232695139912</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.6831144560204427</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.02882390069429834</v>
       </c>
       <c r="U13" t="n">
+        <v>0.6741245531018242</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
         <v>5</v>
       </c>
-      <c r="V13" t="n">
+      <c r="Z13" t="n">
         <v>3</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AA13" t="n">
         <v>9</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH13" t="n">
         <v>55</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z13" t="n">
+      <c r="AI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>43</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AK13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1629,39 +2039,69 @@
         <v>0.5531827499159332</v>
       </c>
       <c r="P14" t="n">
+        <v>0.04824016563146998</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.64976773812144</v>
+      </c>
+      <c r="R14" t="n">
         <v>0.04371184371184371</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.5394412273047411</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>0.03101343101343101</v>
       </c>
       <c r="U14" t="n">
+        <v>0.6632802630337851</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
         <v>5</v>
       </c>
-      <c r="V14" t="n">
+      <c r="Z14" t="n">
         <v>3</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AA14" t="n">
         <v>10</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH14" t="n">
         <v>52</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AI14" t="n">
         <v>4</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AJ14" t="n">
         <v>39</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AK14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1714,39 +2154,69 @@
         <v>0.04135914276928322</v>
       </c>
       <c r="P15" t="n">
+        <v>0.2214677811143201</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.0284098048449859</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.1483273721859878</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.03047537217672465</v>
       </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
+        <v>0.1466442247001894</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.03241121792440683</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="X15" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
+      <c r="Y15" t="n">
         <v>8</v>
       </c>
-      <c r="V15" t="n">
+      <c r="Z15" t="n">
         <v>6</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AA15" t="n">
         <v>16</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH15" t="n">
         <v>55</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z15" t="n">
+      <c r="AI15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>43</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AK15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1799,39 +2269,69 @@
         <v>0.7651839987109404</v>
       </c>
       <c r="P16" t="n">
+        <v>0.006167157584683358</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.9521933754290275</v>
+      </c>
+      <c r="R16" t="n">
         <v>-0.02018900343642612</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.7695487264404447</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.0008591065292096221</v>
       </c>
       <c r="U16" t="n">
+        <v>0.9900533454687662</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
         <v>6</v>
       </c>
-      <c r="V16" t="n">
-        <v>1</v>
-      </c>
-      <c r="W16" t="n">
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="n">
         <v>12</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH16" t="n">
         <v>27</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AI16" t="n">
         <v>29</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AJ16" t="n">
         <v>19</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AK16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1884,39 +2384,69 @@
         <v>0.6732884481156822</v>
       </c>
       <c r="P17" t="n">
+        <v>0.06680683667932717</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.5178137129208193</v>
+      </c>
+      <c r="R17" t="n">
         <v>0.02719298245614035</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.6946969935927938</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.04385964912280701</v>
       </c>
       <c r="U17" t="n">
+        <v>0.5267031786780156</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
         <v>5</v>
       </c>
-      <c r="V17" t="n">
+      <c r="Z17" t="n">
         <v>5</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AA17" t="n">
         <v>11</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH17" t="n">
         <v>24</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AI17" t="n">
         <v>32</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AJ17" t="n">
         <v>15</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AK17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1969,39 +2499,69 @@
         <v>0.9332814399326592</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.05632653061224489</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.5797403010291713</v>
+      </c>
+      <c r="R18" t="n">
         <v>-0.005978148835291693</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.930138227885474</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>-0.03195217480931767</v>
       </c>
       <c r="U18" t="n">
+        <v>0.6393655957518254</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
         <v>5</v>
       </c>
-      <c r="V18" t="n">
+      <c r="Z18" t="n">
         <v>4</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AA18" t="n">
         <v>10</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH18" t="n">
         <v>24</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AI18" t="n">
         <v>32</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AJ18" t="n">
         <v>20</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AK18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2054,39 +2614,69 @@
         <v>0.2713432263568843</v>
       </c>
       <c r="P19" t="n">
+        <v>-0.1413998914812805</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1693804707106866</v>
+      </c>
+      <c r="R19" t="n">
         <v>-0.06929824561403508</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>0.3172070960462492</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>-0.0907894736842105</v>
       </c>
       <c r="U19" t="n">
+        <v>0.1900583326478065</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
         <v>4</v>
       </c>
-      <c r="V19" t="n">
+      <c r="Z19" t="n">
         <v>2</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AA19" t="n">
         <v>7</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH19" t="n">
         <v>27</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AI19" t="n">
         <v>29</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AJ19" t="n">
         <v>29</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AK19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Analysis 2025.xlsx
+++ b/Analysis 2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK19"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2226,80 +2226,80 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025 Llama-Abstract-100</t>
+          <t>2025 Llama-Full Text-Zeroshot</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.7319587628865979</v>
+        <v>2.16</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8247422680412371</v>
+        <v>2.11</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7835051546391752</v>
+        <v>2.77</v>
       </c>
       <c r="F16" t="n">
-        <v>6.185567010309279</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9690721649484536</v>
+        <v>2.56</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8535096645355225</v>
+        <v>0.8466761708259583</v>
       </c>
       <c r="I16" t="n">
-        <v>0.88007652759552</v>
+        <v>0.8673069477081299</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8663458824157715</v>
+        <v>0.856656014919281</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8207377195358276</v>
+        <v>0.803662121295929</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8467504978179932</v>
+        <v>0.8545398712158203</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8332484364509583</v>
+        <v>0.8281151056289673</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.03071744161582158</v>
+        <v>0.2234023402340234</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7651839987109404</v>
+        <v>0.02546635626445397</v>
       </c>
       <c r="P16" t="n">
-        <v>0.006167157584683358</v>
+        <v>0.1564116411641164</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9521933754290275</v>
+        <v>0.1201765551636529</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.02018900343642612</v>
+        <v>0.1486868686868687</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7695487264404447</v>
+        <v>0.02838716462397863</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0008591065292096221</v>
+        <v>0.1042424242424242</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9900533454687662</v>
+        <v>0.1243647668827246</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
         <v>12</v>
@@ -2308,28 +2308,28 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
         <v>6</v>
       </c>
       <c r="AF16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="AI16" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2341,110 +2341,110 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025 Llama-Summary-100</t>
+          <t>2025 Llama-Full Text-Oneshot</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.6770833333333334</v>
+        <v>1.552083333333333</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8020833333333334</v>
+        <v>1.958333333333333</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6145833333333334</v>
+        <v>2.229166666666667</v>
       </c>
       <c r="F17" t="n">
-        <v>6.21875</v>
+        <v>11.11458333333333</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8541666666666666</v>
+        <v>1.979166666666667</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8546110987663269</v>
+        <v>0.8656818270683289</v>
       </c>
       <c r="I17" t="n">
-        <v>0.882559061050415</v>
+        <v>0.8673297762870789</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8681354522705078</v>
+        <v>0.8663153648376465</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8194912075996399</v>
+        <v>0.8180727362632751</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8481839299201965</v>
+        <v>0.8603906631469727</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8332781791687012</v>
+        <v>0.8384786248207092</v>
       </c>
       <c r="N17" t="n">
-        <v>0.04358383071079761</v>
+        <v>0.1364487249050461</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6732884481156822</v>
+        <v>0.1849671429919719</v>
       </c>
       <c r="P17" t="n">
-        <v>0.06680683667932717</v>
+        <v>0.1256375474769398</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.5178137129208193</v>
+        <v>0.2225764193966726</v>
       </c>
       <c r="R17" t="n">
-        <v>0.02719298245614035</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6946969935927938</v>
+        <v>0.1489229247512205</v>
       </c>
       <c r="T17" t="n">
-        <v>0.04385964912280701</v>
+        <v>0.08245614035087717</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5267031786780156</v>
+        <v>0.2339962025860411</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG17" t="n">
         <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="AI17" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AJ17" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2456,65 +2456,65 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025 Llama-Abstract-1000</t>
+          <t>2025 Llama-Abstract-100</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.7373737373737373</v>
+        <v>0.7319587628865979</v>
       </c>
       <c r="D18" t="n">
-        <v>0.797979797979798</v>
+        <v>0.8247422680412371</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6868686868686869</v>
+        <v>0.7835051546391752</v>
       </c>
       <c r="F18" t="n">
-        <v>5.252525252525253</v>
+        <v>6.185567010309279</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.9690721649484536</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8521520495414734</v>
+        <v>0.8535096645355225</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8811490535736084</v>
+        <v>0.88007652759552</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8661757707595825</v>
+        <v>0.8663458824157715</v>
       </c>
       <c r="K18" t="n">
-        <v>0.813251793384552</v>
+        <v>0.8207377195358276</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8406529426574707</v>
+        <v>0.8467504978179932</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8264533877372742</v>
+        <v>0.8332484364509583</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.008521954236239949</v>
+        <v>-0.03071744161582158</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9332814399326592</v>
+        <v>0.7651839987109404</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.05632653061224489</v>
+        <v>0.006167157584683358</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5797403010291713</v>
+        <v>0.9521933754290275</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.005978148835291693</v>
+        <v>-0.02018900343642612</v>
       </c>
       <c r="S18" t="n">
-        <v>0.930138227885474</v>
+        <v>0.7695487264404447</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.03195217480931767</v>
+        <v>0.0008591065292096221</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6393655957518254</v>
+        <v>0.9900533454687662</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -2523,16 +2523,16 @@
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2541,25 +2541,25 @@
         <v>1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>6</v>
       </c>
       <c r="AF18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG18" t="n">
         <v>11</v>
       </c>
       <c r="AH18" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI18" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AJ18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -2571,112 +2571,342 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>2025 Llama-Summary-100</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6770833333333334</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.8020833333333334</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6145833333333334</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.21875</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8546110987663269</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.882559061050415</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.8681354522705078</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.8194912075996399</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.8481839299201965</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.8332781791687012</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.04358383071079761</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.6732884481156822</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.06680683667932717</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.5178137129208193</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.02719298245614035</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.6946969935927938</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.04385964912280701</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.5267031786780156</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025 Llama-Abstract-1000</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7373737373737373</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.797979797979798</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6868686868686869</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5.252525252525253</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8521520495414734</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8811490535736084</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8661757707595825</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.813251793384552</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.8406529426574707</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.8264533877372742</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.008521954236239949</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.9332814399326592</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.05632653061224489</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.5797403010291713</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.005978148835291693</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.930138227885474</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.03195217480931767</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.6393655957518254</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>2025 Llama Time Finetuned</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C21" t="n">
         <v>0.7291666666666666</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D21" t="n">
         <v>0.7291666666666666</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E21" t="n">
         <v>0.8125</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F21" t="n">
         <v>4.90625</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G21" t="n">
         <v>1.083333333333333</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H21" t="n">
         <v>0.855548083782196</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I21" t="n">
         <v>0.8776938319206238</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J21" t="n">
         <v>0.8662011027336121</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K21" t="n">
         <v>0.8195622563362122</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L21" t="n">
         <v>0.8462507724761963</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M21" t="n">
         <v>0.8324375748634338</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N21" t="n">
         <v>-0.1133884970157352</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O21" t="n">
         <v>0.2713432263568843</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P21" t="n">
         <v>-0.1413998914812805</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q21" t="n">
         <v>0.1693804707106866</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R21" t="n">
         <v>-0.06929824561403508</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S21" t="n">
         <v>0.3172070960462492</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T21" t="n">
         <v>-0.0907894736842105</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U21" t="n">
         <v>0.1900583326478065</v>
       </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="n">
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
         <v>4</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="Z21" t="n">
         <v>2</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AA21" t="n">
         <v>7</v>
       </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE19" t="n">
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE21" t="n">
         <v>4</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AF21" t="n">
         <v>2</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AG21" t="n">
         <v>7</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AH21" t="n">
         <v>27</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AI21" t="n">
         <v>29</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AJ21" t="n">
         <v>29</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AK21" t="n">
         <v>0</v>
       </c>
     </row>
